--- a/results/Int All Data -0.0/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.0/Linea_fi_explain.xlsx
@@ -1694,10 +1694,10 @@
         <v>0.005717730071255544</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01895475655600837</v>
+        <v>0.01895811338715976</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008939472843750174</v>
+        <v>0.008942822927502267</v>
       </c>
       <c r="J3" t="n">
         <v>0.001791154225372436</v>
@@ -1712,7 +1712,7 @@
         <v>0.002219476035114788</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006827417360218334</v>
+        <v>0.006824060529066941</v>
       </c>
       <c r="O3" t="n">
         <v>0.003339452455130855</v>
@@ -1736,7 +1736,7 @@
         <v>4.950198884452512e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008942822927502267</v>
+        <v>0.008942933051362631</v>
       </c>
       <c r="W3" t="n">
         <v>0.00201347896308622</v>
@@ -1781,7 +1781,7 @@
         <v>0.02189277195467246</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02205618465119333</v>
+        <v>0.02205964485880578</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01645448774679798</v>
@@ -1892,13 +1892,13 @@
         <v>0.006259630024302967</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0008273471515450458</v>
+        <v>-0.0008241213450934336</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0005615059620183605</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.002282573958777657</v>
+        <v>0.002279057784375407</v>
       </c>
       <c r="BY3" t="n">
         <v>0.002397559032646442</v>
@@ -1910,10 +1910,10 @@
         <v>0.006937496194958055</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.005779041049879803</v>
+        <v>0.005775524875477553</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.008601390972445919</v>
+        <v>0.008605113980636538</v>
       </c>
       <c r="CD3" t="n">
         <v>0.003881950984291406</v>
@@ -1922,7 +1922,7 @@
         <v>-6.939226320586971e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0005333577530588663</v>
+        <v>-0.0005370807612494843</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4207278985996998</v>
@@ -1949,7 +1949,7 @@
         <v>-0.0004280574638426229</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.02674407314865592</v>
+        <v>0.02674055697425367</v>
       </c>
       <c r="CP3" t="n">
         <v>7.909266883439182e-05</v>
@@ -1964,7 +1964,7 @@
         <v>0.3439097527999233</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.08859865350108413</v>
+        <v>0.08860200358483623</v>
       </c>
       <c r="CU3" t="n">
         <v>0.1061856080039387</v>
@@ -1988,7 +1988,7 @@
         <v>0.001392412597316352</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001079950427876533</v>
+        <v>0.001079854226114502</v>
       </c>
       <c r="DC3" t="n">
         <v>0.2835581395732251</v>
@@ -2024,19 +2024,19 @@
         <v>-0.003231184524655559</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.001199370422675906</v>
+        <v>0.001196105649577637</v>
       </c>
       <c r="DO3" t="n">
         <v>-0.0007353043988533425</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001619099390411217</v>
+        <v>-0.0016153763822206</v>
       </c>
       <c r="DQ3" t="n">
+        <v>-5.890931343302654e-05</v>
+      </c>
+      <c r="DR3" t="n">
         <v>-5.543588515932064e-05</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>-5.890931343302654e-05</v>
       </c>
       <c r="DS3" t="n">
         <v>0.001341377925565557</v>
@@ -2111,7 +2111,7 @@
         <v>0.002181804467557097</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01883037877859451</v>
+        <v>0.01883389495299676</v>
       </c>
       <c r="ER3" t="n">
         <v>0.0002495068101247288</v>
@@ -2163,10 +2163,10 @@
         <v>0.007782805528176112</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01691006854296679</v>
+        <v>0.01691442001113162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01030992096510417</v>
+        <v>0.01031335067821907</v>
       </c>
       <c r="J4" t="n">
         <v>0.01308689678804792</v>
@@ -2181,7 +2181,7 @@
         <v>0.004999067050628436</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006920406635915464</v>
+        <v>0.006916549062848792</v>
       </c>
       <c r="O4" t="n">
         <v>0.006286728678393564</v>
@@ -2205,7 +2205,7 @@
         <v>0.007798137555828308</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01031335067821907</v>
+        <v>0.01030882539253736</v>
       </c>
       <c r="W4" t="n">
         <v>0.006244426163510083</v>
@@ -2250,7 +2250,7 @@
         <v>0.0181885151931793</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01372643256708421</v>
+        <v>0.01372307905164078</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01590360070891493</v>
@@ -2361,13 +2361,13 @@
         <v>0.01384620311363195</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004841992118757621</v>
+        <v>0.00484266300929034</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0009206017191133492</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01087114038458387</v>
+        <v>0.01087074064260373</v>
       </c>
       <c r="BY4" t="n">
         <v>0.002048303818321554</v>
@@ -2379,10 +2379,10 @@
         <v>0.008878296630437715</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.00992608403844202</v>
+        <v>0.009928558314457889</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.008958431497654747</v>
+        <v>0.008959848250370727</v>
       </c>
       <c r="CD4" t="n">
         <v>0.006831307368735596</v>
@@ -2391,7 +2391,7 @@
         <v>0.002750224092988303</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002187116469277623</v>
+        <v>0.002193383279341272</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1044551843110386</v>
@@ -2418,7 +2418,7 @@
         <v>0.007078704331055636</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.02745426520275591</v>
+        <v>0.02745139820871205</v>
       </c>
       <c r="CP4" t="n">
         <v>0.0004724113839295273</v>
@@ -2433,7 +2433,7 @@
         <v>0.1262128425329507</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.07744643457841094</v>
+        <v>0.07743969060628575</v>
       </c>
       <c r="CU4" t="n">
         <v>0.03916443936833313</v>
@@ -2457,7 +2457,7 @@
         <v>0.002237608313296756</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.007830297235022167</v>
+        <v>0.007829057946218463</v>
       </c>
       <c r="DC4" t="n">
         <v>0.0884444397494481</v>
@@ -2493,19 +2493,19 @@
         <v>0.008049546593339368</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002231640929770043</v>
+        <v>0.002234249684437074</v>
       </c>
       <c r="DO4" t="n">
         <v>0.006163431025667926</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.01104821191112508</v>
+        <v>0.01103755599010893</v>
       </c>
       <c r="DQ4" t="n">
+        <v>0.0004631758218462011</v>
+      </c>
+      <c r="DR4" t="n">
         <v>0.0004606061703645714</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>0.0004631758218462011</v>
       </c>
       <c r="DS4" t="n">
         <v>0.003619635768817484</v>
@@ -2580,7 +2580,7 @@
         <v>0.007679113242284703</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.04670990931541308</v>
+        <v>0.04670938850955067</v>
       </c>
       <c r="ER4" t="n">
         <v>0.002448281682326935</v>
@@ -2902,7 +2902,7 @@
         <v>0.06043551088777217</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.05172529313232831</v>
+        <v>-0.05169179229480737</v>
       </c>
       <c r="CU5" t="n">
         <v>0.03745161290322585</v>
@@ -2968,7 +2968,7 @@
         <v>-0.01102010424422937</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.03008190618019364</v>
+        <v>-0.03004467609828746</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0.0009030913511636318</v>
@@ -3143,7 +3143,7 @@
         <v>-0.004397440374075826</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001733881564539472</v>
+        <v>0.001742532083570614</v>
       </c>
       <c r="W6" t="n">
         <v>-0.0001054055999646225</v>
@@ -3188,7 +3188,7 @@
         <v>0.00627029148288622</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01140792226603362</v>
+        <v>0.01143387382312704</v>
       </c>
       <c r="AL6" t="n">
         <v>0.005173934187064364</v>
@@ -3768,7 +3768,7 @@
         <v>0.00212380300957592</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.741980853865459e-05</v>
+        <v>8.354884079671554e-05</v>
       </c>
       <c r="BW7" t="n">
         <v>0.0004522950435291661</v>
@@ -3789,7 +3789,7 @@
         <v>0.001866268909221902</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.009682013202131018</v>
+        <v>0.009700628243084108</v>
       </c>
       <c r="CD7" t="n">
         <v>0.002288826978802455</v>
@@ -3864,7 +3864,7 @@
         <v>0.001157718352007964</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.003037099635123714</v>
+        <v>0.003054199498324811</v>
       </c>
       <c r="DC7" t="n">
         <v>0.2859981016314331</v>
@@ -4042,7 +4042,7 @@
         <v>0.03141967620572357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01670442682511587</v>
+        <v>0.01672955245325658</v>
       </c>
       <c r="J8" t="n">
         <v>0.007861237541049709</v>
@@ -4081,7 +4081,7 @@
         <v>0.001388227501774933</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01672955245325658</v>
+        <v>0.01670442682511587</v>
       </c>
       <c r="W8" t="n">
         <v>0.004737275998011593</v>
@@ -4243,7 +4243,7 @@
         <v>0.001139133831900913</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.003338480120336046</v>
+        <v>0.003312108812319167</v>
       </c>
       <c r="BY8" t="n">
         <v>0.003299017606225821</v>
@@ -4294,7 +4294,7 @@
         <v>0.004482587480738188</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.05051595187811832</v>
+        <v>0.05050716144211269</v>
       </c>
       <c r="CP8" t="n">
         <v>0.000472293395540957</v>
@@ -4456,7 +4456,7 @@
         <v>0.0003856036657125861</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.02027600834807862</v>
+        <v>0.02028479878408424</v>
       </c>
       <c r="ER8" t="n">
         <v>9.460509004074746e-05</v>
